--- a/Phoenix Compass/education compass/tools/feishu-v05/Phoenix_Feishu_Operating_Model_V0.5.1_Master.xlsx
+++ b/Phoenix Compass/education compass/tools/feishu-v05/Phoenix_Feishu_Operating_Model_V0.5.1_Master.xlsx
@@ -17,7 +17,8 @@
     <sheet name="Service_Projects" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Deliveries" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Settlements" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Integration_Links" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Schools" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Integration_Links" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -458,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -620,304 +621,262 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>表</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>主字段</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>列数</t>
-        </is>
-      </c>
+          <t>草案（未经业务确认）</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="n"/>
       <c r="D14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Family_Student_View</t>
+          <t>Schools</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Client ID</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>18</v>
-      </c>
+          <t>照飞书现有表结构收入母版。docx 只要求 School 语义独立于 Partner，未规定独立建表。未决：Deliveries 的 School Subject Ref 是否改为引用 Schools.School ID；学校返佣从 Application 还是从 School 侧起算。</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Partners</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Partner ID</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>23</v>
-      </c>
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Products_Services</t>
+          <t>表</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Product ID</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>17</v>
+          <t>主字段</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>列数</t>
+        </is>
       </c>
       <c r="D17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Deals</t>
+          <t>Family_Student_View</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Deal ID</t>
+          <t>Client ID</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Contracts</t>
+          <t>Partners</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Contract ID</t>
+          <t>Partner ID</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Products_Services</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Payment ID</t>
+          <t>Product ID</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Service_Projects</t>
+          <t>Deals</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Service Project ID</t>
+          <t>Deal ID</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Deliveries</t>
+          <t>Contracts</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Delivery Record ID</t>
+          <t>Contract ID</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Settlements</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Settlement ID</t>
+          <t>Payment ID</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Integration_Links</t>
+          <t>Service_Projects</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Integration Link ID</t>
+          <t>Service Project ID</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D24" s="2" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Deliveries</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Delivery Record ID</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>48</v>
+      </c>
       <c r="D25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>飞书新增列的逐列裁定</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr"/>
-      <c r="C26" s="2" t="inlineStr"/>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Settlement ID</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>27</v>
+      </c>
       <c r="D26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>原表</t>
+          <t>Schools（草案）</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>列</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>处理</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>理由</t>
-        </is>
-      </c>
+          <t>School ID</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Partners</t>
+          <t>Integration_Links</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Agreement Ref</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>采纳</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>底稿只有 Commission Rule ID，没有合作协议引用</t>
-        </is>
-      </c>
+          <t>Integration Link ID</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D28" s="2" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Partners</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Source Owner Type</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>丢弃</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>底稿 Source Owner 已表达原始归属，docx 未要求再拆类型</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Partners</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Source Owner ID</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>丢弃</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>同上，避免与 Source Owner 语义重复</t>
-        </is>
-      </c>
+          <t>飞书新增列的逐列裁定</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Partners</t>
+          <t>原表</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Created At</t>
+          <t>列</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>采纳</t>
+          <t>处理</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>审计时间戳，底稿在 Deals 上已有此惯例</t>
+          <t>理由</t>
         </is>
       </c>
     </row>
@@ -929,7 +888,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Updated At</t>
+          <t>Agreement Ref</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -939,19 +898,19 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>底稿只有 Commission Rule ID，没有合作协议引用</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Products_Services</t>
+          <t>Partners</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Record ID</t>
+          <t>Source Owner Type</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -961,19 +920,19 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>与 Product ID 重复</t>
+          <t>底稿 Source Owner 已表达原始归属，docx 未要求再拆类型</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Products_Services</t>
+          <t>Partners</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Record Type</t>
+          <t>Source Owner ID</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -983,51 +942,51 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>父子结构本次不做</t>
+          <t>同上，避免与 Source Owner 语义重复</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Products_Services</t>
+          <t>Partners</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Package ID</t>
+          <t>Created At</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>采纳</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>父子结构本次不做</t>
+          <t>审计时间戳，底稿在 Deals 上已有此惯例</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Products_Services</t>
+          <t>Partners</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Service ID</t>
+          <t>Updated At</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>采纳</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>父子结构本次不做</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
@@ -1039,7 +998,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Record ID</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1061,7 +1020,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Record Type</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1071,7 +1030,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>与 Product Name 重复</t>
+          <t>父子结构本次不做</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1042,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Delivery Unit</t>
+          <t>Package ID</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1093,7 +1052,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>与 Unit 重复</t>
+          <t>父子结构本次不做</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1064,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Included Quantity</t>
+          <t>Service ID</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1127,7 +1086,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Parent Record Ref</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1137,19 +1096,19 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>父子结构本次不做</t>
+          <t>与 Product ID 重复</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Products_Services</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Delivery ID</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1159,19 +1118,19 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>与 Delivery Event ID 重复</t>
+          <t>与 Product Name 重复</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Products_Services</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Service ID</t>
+          <t>Delivery Unit</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1181,19 +1140,19 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>依附于已放弃的父子结构</t>
+          <t>与 Unit 重复</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Products_Services</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Milestone Type</t>
+          <t>Included Quantity</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1203,29 +1162,29 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Delivery Type 的 MILESTONE 取值已覆盖</t>
+          <t>父子结构本次不做</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Products_Services</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Total Quantity</t>
+          <t>Parent Record Ref</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>采纳</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>应交付总量，底稿只有已交付的 Units Delivered</t>
+          <t>父子结构本次不做</t>
         </is>
       </c>
     </row>
@@ -1237,17 +1196,17 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Delivery ID</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>采纳</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>合并后需要统一的负责人列</t>
+          <t>与 Delivery Event ID 重复</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1218,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Completed At</t>
+          <t>Service ID</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1269,7 +1228,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>与 Delivered At 重复</t>
+          <t>依附于已放弃的父子结构</t>
         </is>
       </c>
     </row>
@@ -1281,73 +1240,73 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Updated At</t>
+          <t>Milestone Type</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>采纳</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>审计时间戳</t>
+          <t>Delivery Type 的 MILESTONE 取值已覆盖</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Delivery</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>School Role</t>
+          <t>Total Quantity</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>采纳</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>与 School Role Ref 重复</t>
+          <t>应交付总量，底稿只有已交付的 Units Delivered</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Delivery</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>School Ref</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>采纳</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>与 School Subject Ref 重复</t>
+          <t>合并后需要统一的负责人列</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Delivery</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Consent Snapshot</t>
+          <t>Completed At</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -1357,19 +1316,19 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>docx 要求只在必要时引用 consent_id，不留快照</t>
+          <t>与 Delivered At 重复</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Delivery</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Offer Received At</t>
+          <t>Updated At</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -1379,7 +1338,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>底稿只有 Offer Date，里程碑时间补全</t>
+          <t>审计时间戳</t>
         </is>
       </c>
     </row>
@@ -1391,17 +1350,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Deposit Paid At</t>
+          <t>School Role</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>采纳</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>与 School Role Ref 重复</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1372,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Enrolled At</t>
+          <t>School Ref</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>采纳</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>与 School Subject Ref 重复</t>
         </is>
       </c>
     </row>
@@ -1435,17 +1394,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Created At</t>
+          <t>Consent Snapshot</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>采纳</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>审计时间戳</t>
+          <t>docx 要求只在必要时引用 consent_id，不留快照</t>
         </is>
       </c>
     </row>
@@ -1457,105 +1416,105 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Updated At</t>
+          <t>Offer Received At</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>采纳</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Delivery 侧已采纳同名列，合并后只留一个</t>
+          <t>底稿只有 Offer Date，里程碑时间补全</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Settlements</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Money Type</t>
+          <t>Deposit Paid At</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>改名</t>
+          <t>采纳</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>docx 指定用 Settlement Type 区分四类资金</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Settlements</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Business Basis Key</t>
+          <t>Enrolled At</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>采纳</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>底稿 Source Ref Type + Source Ref ID 已表达业务依据</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Settlements</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Beneficiary / Counterparty ID</t>
+          <t>Created At</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>采纳</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>与 Counterparty Subject Ref 重复</t>
+          <t>审计时间戳</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Settlements</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Period Start</t>
+          <t>Updated At</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>采纳</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>结算周期，底稿没有</t>
+          <t>Delivery 侧已采纳同名列，合并后只留一个</t>
         </is>
       </c>
     </row>
@@ -1567,37 +1526,125 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Period End</t>
+          <t>Money Type</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>采纳</t>
+          <t>改名</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>docx 指定用 Settlement Type 区分四类资金</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Business Basis Key</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>丢弃</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>底稿 Source Ref Type + Source Ref ID 已表达业务依据</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Beneficiary / Counterparty ID</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>丢弃</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>与 Counterparty Subject Ref 重复</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Period Start</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>结算周期，底稿没有</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Period End</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
           <t>Integration_Links</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>采纳</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>docx 点名要求的列，底稿没有</t>
         </is>
@@ -1902,6 +1949,155 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>School ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>School Code</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>School Name</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>School Type</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Cooperation Status</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Account Manager</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Agreement Ref</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Commission Eligible</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Created At</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Updated At</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>PN-SCH-0001</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>SCH-HK-0001</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>示例大学</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>UNIVERSITY</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Katrina</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr"/>
+      <c r="I2" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr"/>
+      <c r="L2" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"HIGH_SCHOOL,UNIVERSITY,GRADUATE_SCHOOL,OTHER"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PROSPECTING,NEGOTIATING,SIGNED,ACTIVE,PAUSED,TERMINATED"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ACTIVE,INACTIVE,DRAFT,ARCHIVED"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Phoenix Compass/education compass/tools/feishu-v05/Phoenix_Feishu_Operating_Model_V0.5.1_Master.xlsx
+++ b/Phoenix Compass/education compass/tools/feishu-v05/Phoenix_Feishu_Operating_Model_V0.5.1_Master.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D25" s="2" t="n"/>
     </row>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D27" s="2" t="n"/>
     </row>
@@ -1521,56 +1521,56 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Settlements</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Money Type</t>
+          <t>School Subject Ref</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>改名</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>docx 指定用 Settlement Type 区分四类资金</t>
+          <t>机构主体 ID 移到 Schools.Subject Ref</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Settlements</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Business Basis Key</t>
+          <t>School Role Ref</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>改名</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>底稿 Source Ref Type + Source Ref ID 已表达业务依据</t>
+          <t>改为引用 Schools.School ID</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Settlements</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Beneficiary / Counterparty ID</t>
+          <t>School Name</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>与 Counterparty Subject Ref 重复</t>
+          <t>学校名称只在 Schools 维护，申请侧可用查找列显示</t>
         </is>
       </c>
     </row>
@@ -1592,17 +1592,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Period Start</t>
+          <t>Money Type</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>采纳</t>
+          <t>改名</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>结算周期，底稿没有</t>
+          <t>docx 指定用 Settlement Type 区分四类资金</t>
         </is>
       </c>
     </row>
@@ -1614,37 +1614,103 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Period End</t>
+          <t>Business Basis Key</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>采纳</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>底稿 Source Ref Type + Source Ref ID 已表达业务依据</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Beneficiary / Counterparty ID</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>丢弃</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>与 Counterparty Subject Ref 重复</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Period Start</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>结算周期，底稿没有</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Period End</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
           <t>Integration_Links</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>采纳</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>docx 点名要求的列，底稿没有</t>
         </is>
@@ -1954,21 +2020,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1979,55 +2047,65 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
+          <t>Subject Type</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Subject Ref</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
           <t>School Code</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>School Name</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>School Type</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Cooperation Status</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Account Manager</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Agreement Ref</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Commission Eligible</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Created At</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Updated At</t>
         </is>
@@ -2041,55 +2119,68 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
+          <t>ORGANIZATION</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>ORG-REF-0001</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
           <t>SCH-HK-0001</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>示例大学</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>UNIVERSITY</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>Katrina</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="5" t="b">
+      <c r="J2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr"/>
-      <c r="L2" s="5" t="inlineStr"/>
+      <c r="M2" s="5" t="inlineStr"/>
+      <c r="N2" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ORGANIZATION,PERSON"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"HIGH_SCHOOL,UNIVERSITY,GRADUATE_SCHOOL,OTHER"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PROSPECTING,NEGOTIATING,SIGNED,ACTIVE,PAUSED,TERMINATED"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ACTIVE,INACTIVE,DRAFT,ARCHIVED"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3785,7 +3876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV2"/>
+  <dimension ref="A1:AT2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3810,32 +3901,30 @@
     <col width="25" customWidth="1" min="20" max="20"/>
     <col width="22" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="24" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
     <col width="21" customWidth="1" min="24" max="24"/>
-    <col width="17" customWidth="1" min="25" max="25"/>
-    <col width="21" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="23" customWidth="1" min="28" max="28"/>
-    <col width="24" customWidth="1" min="29" max="29"/>
-    <col width="20" customWidth="1" min="30" max="30"/>
-    <col width="26" customWidth="1" min="31" max="31"/>
-    <col width="16" customWidth="1" min="32" max="32"/>
-    <col width="18" customWidth="1" min="33" max="33"/>
-    <col width="24" customWidth="1" min="34" max="34"/>
-    <col width="32" customWidth="1" min="35" max="35"/>
-    <col width="18" customWidth="1" min="36" max="36"/>
-    <col width="16" customWidth="1" min="37" max="37"/>
-    <col width="20" customWidth="1" min="38" max="38"/>
-    <col width="22" customWidth="1" min="39" max="39"/>
-    <col width="31" customWidth="1" min="40" max="40"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="23" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="20" customWidth="1" min="28" max="28"/>
+    <col width="26" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
+    <col width="18" customWidth="1" min="31" max="31"/>
+    <col width="24" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="34" max="34"/>
+    <col width="16" customWidth="1" min="35" max="35"/>
+    <col width="20" customWidth="1" min="36" max="36"/>
+    <col width="22" customWidth="1" min="37" max="37"/>
+    <col width="31" customWidth="1" min="38" max="38"/>
+    <col width="14" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="40" max="40"/>
     <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="20" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="16" customWidth="1" min="44" max="44"/>
-    <col width="23" customWidth="1" min="45" max="45"/>
-    <col width="21" customWidth="1" min="46" max="46"/>
-    <col width="17" customWidth="1" min="47" max="47"/>
-    <col width="16" customWidth="1" min="48" max="48"/>
+    <col width="16" customWidth="1" min="42" max="42"/>
+    <col width="23" customWidth="1" min="43" max="43"/>
+    <col width="21" customWidth="1" min="44" max="44"/>
+    <col width="17" customWidth="1" min="45" max="45"/>
+    <col width="16" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3951,130 +4040,120 @@
       </c>
       <c r="W1" s="4" t="inlineStr">
         <is>
-          <t>School Subject Ref</t>
+          <t>School ID</t>
         </is>
       </c>
       <c r="X1" s="4" t="inlineStr">
         <is>
-          <t>School Role Ref</t>
+          <t>Program / Major</t>
         </is>
       </c>
       <c r="Y1" s="4" t="inlineStr">
         <is>
-          <t>School Name</t>
+          <t>Intake</t>
         </is>
       </c>
       <c r="Z1" s="4" t="inlineStr">
         <is>
-          <t>Program / Major</t>
+          <t>Application Round</t>
         </is>
       </c>
       <c r="AA1" s="4" t="inlineStr">
         <is>
-          <t>Intake</t>
+          <t>Application Status</t>
         </is>
       </c>
       <c r="AB1" s="4" t="inlineStr">
         <is>
-          <t>Application Round</t>
+          <t>Internal Owner</t>
         </is>
       </c>
       <c r="AC1" s="4" t="inlineStr">
         <is>
-          <t>Application Status</t>
+          <t>Data Package Version</t>
         </is>
       </c>
       <c r="AD1" s="4" t="inlineStr">
         <is>
-          <t>Internal Owner</t>
+          <t>Consent ID</t>
         </is>
       </c>
       <c r="AE1" s="4" t="inlineStr">
         <is>
-          <t>Data Package Version</t>
+          <t>Submitted At</t>
         </is>
       </c>
       <c r="AF1" s="4" t="inlineStr">
         <is>
-          <t>Consent ID</t>
+          <t>Submission Channel</t>
         </is>
       </c>
       <c r="AG1" s="4" t="inlineStr">
         <is>
-          <t>Submitted At</t>
+          <t>School Portal Ref / Receipt</t>
         </is>
       </c>
       <c r="AH1" s="4" t="inlineStr">
         <is>
-          <t>Submission Channel</t>
+          <t>Offer Status</t>
         </is>
       </c>
       <c r="AI1" s="4" t="inlineStr">
         <is>
-          <t>School Portal Ref / Receipt</t>
+          <t>Offer Date</t>
         </is>
       </c>
       <c r="AJ1" s="4" t="inlineStr">
         <is>
-          <t>Offer Status</t>
+          <t>Deposit Status</t>
         </is>
       </c>
       <c r="AK1" s="4" t="inlineStr">
         <is>
-          <t>Offer Date</t>
+          <t>Enrolment Status</t>
         </is>
       </c>
       <c r="AL1" s="4" t="inlineStr">
         <is>
-          <t>Deposit Status</t>
+          <t>School Commission Trigger</t>
         </is>
       </c>
       <c r="AM1" s="4" t="inlineStr">
         <is>
-          <t>Enrolment Status</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="AN1" s="4" t="inlineStr">
         <is>
-          <t>School Commission Trigger</t>
+          <t>Total Quantity</t>
         </is>
       </c>
       <c r="AO1" s="4" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="AP1" s="4" t="inlineStr">
         <is>
-          <t>Total Quantity</t>
+          <t>Updated At</t>
         </is>
       </c>
       <c r="AQ1" s="4" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Offer Received At</t>
         </is>
       </c>
       <c r="AR1" s="4" t="inlineStr">
         <is>
-          <t>Updated At</t>
+          <t>Deposit Paid At</t>
         </is>
       </c>
       <c r="AS1" s="4" t="inlineStr">
         <is>
-          <t>Offer Received At</t>
+          <t>Enrolled At</t>
         </is>
       </c>
       <c r="AT1" s="4" t="inlineStr">
-        <is>
-          <t>Deposit Paid At</t>
-        </is>
-      </c>
-      <c r="AU1" s="4" t="inlineStr">
-        <is>
-          <t>Enrolled At</t>
-        </is>
-      </c>
-      <c r="AV1" s="4" t="inlineStr">
         <is>
           <t>Created At</t>
         </is>
@@ -4171,69 +4250,61 @@
       </c>
       <c r="W2" s="5" t="inlineStr">
         <is>
-          <t>ORG-REF-0001</t>
+          <t>PN-SCH-0001</t>
         </is>
       </c>
       <c r="X2" s="5" t="inlineStr">
         <is>
-          <t>SCHOOL-ROLE-REF-0001</t>
+          <t>示例专业</t>
         </is>
       </c>
       <c r="Y2" s="5" t="inlineStr">
         <is>
-          <t>示例大学</t>
+          <t>2027-FALL</t>
         </is>
       </c>
       <c r="Z2" s="5" t="inlineStr">
         <is>
-          <t>示例专业</t>
+          <t>ROUND-1</t>
         </is>
       </c>
       <c r="AA2" s="5" t="inlineStr">
         <is>
-          <t>2027-FALL</t>
+          <t>DRAFT</t>
         </is>
       </c>
       <c r="AB2" s="5" t="inlineStr">
         <is>
-          <t>ROUND-1</t>
+          <t>Katrina</t>
         </is>
       </c>
       <c r="AC2" s="5" t="inlineStr">
         <is>
-          <t>DRAFT</t>
-        </is>
-      </c>
-      <c r="AD2" s="5" t="inlineStr">
-        <is>
-          <t>Katrina</t>
-        </is>
-      </c>
-      <c r="AE2" s="5" t="inlineStr">
-        <is>
           <t>1.0</t>
         </is>
       </c>
+      <c r="AD2" s="5" t="inlineStr"/>
+      <c r="AE2" s="5" t="inlineStr"/>
       <c r="AF2" s="5" t="inlineStr"/>
       <c r="AG2" s="5" t="inlineStr"/>
-      <c r="AH2" s="5" t="inlineStr"/>
+      <c r="AH2" s="5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
       <c r="AI2" s="5" t="inlineStr"/>
       <c r="AJ2" s="5" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AK2" s="5" t="inlineStr"/>
-      <c r="AL2" s="5" t="inlineStr">
-        <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="AM2" s="5" t="inlineStr">
+      <c r="AK2" s="5" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
+      <c r="AL2" s="5" t="inlineStr"/>
+      <c r="AM2" s="5" t="inlineStr"/>
       <c r="AN2" s="5" t="inlineStr"/>
       <c r="AO2" s="5" t="inlineStr"/>
       <c r="AP2" s="5" t="inlineStr"/>
@@ -4241,8 +4312,6 @@
       <c r="AR2" s="5" t="inlineStr"/>
       <c r="AS2" s="5" t="inlineStr"/>
       <c r="AT2" s="5" t="inlineStr"/>
-      <c r="AU2" s="5" t="inlineStr"/>
-      <c r="AV2" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="12">
@@ -4267,19 +4336,19 @@
     <dataValidation sqref="R2:R500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PENDING,PASS,FAIL,NOT_REQUIRED"</formula1>
     </dataValidation>
-    <dataValidation sqref="AC2:AC500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AA2:AA500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"DRAFT,WAITING_CLIENT,DATA_COMPLETE,READY_TO_SUBMIT,SUBMITTED,SCHOOL_ACKNOWLEDGED,OFFERED,REJECTED,WITHDRAWN,ENROLLED,CLOSED"</formula1>
     </dataValidation>
+    <dataValidation sqref="AF2:AF500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PORTAL,API,EMAIL,MANUAL,OTHER"</formula1>
+    </dataValidation>
     <dataValidation sqref="AH2:AH500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"PORTAL,API,EMAIL,MANUAL,OTHER"</formula1>
+      <formula1>"NONE,CONDITIONAL,UNCONDITIONAL,REJECTED,WAITLISTED,WITHDRAWN"</formula1>
     </dataValidation>
     <dataValidation sqref="AJ2:AJ500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"NONE,CONDITIONAL,UNCONDITIONAL,REJECTED,WAITLISTED,WITHDRAWN"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AL2:AL500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PENDING,PAID,WAIVED,NOT_REQUIRED,REFUNDED"</formula1>
     </dataValidation>
-    <dataValidation sqref="AM2:AM500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AK2:AK500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PENDING,CONFIRMED,ENROLLED,DEFERRED,CANCELLED"</formula1>
     </dataValidation>
   </dataValidations>
